--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>100925</v>
+        <v>100927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130163680</v>
       </c>
       <c r="B33" t="n">
-        <v>92653</v>
+        <v>92655</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>130163673</v>
       </c>
       <c r="B34" t="n">
-        <v>92653</v>
+        <v>92655</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92653</v>
+        <v>92655</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>88900</v>
+        <v>88987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>100927</v>
+        <v>101014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>88900</v>
+        <v>88987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130163680</v>
+        <v>130163673</v>
       </c>
       <c r="B33" t="n">
-        <v>92655</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472621</v>
+        <v>472642</v>
       </c>
       <c r="R33" t="n">
-        <v>7016967</v>
+        <v>7016959</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130163673</v>
+        <v>130163680</v>
       </c>
       <c r="B34" t="n">
-        <v>92655</v>
+        <v>92742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472642</v>
+        <v>472621</v>
       </c>
       <c r="R34" t="n">
-        <v>7016959</v>
+        <v>7016967</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92655</v>
+        <v>92742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>88900</v>
+        <v>88987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>88986</v>
+        <v>88989</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>101014</v>
+        <v>101017</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>88986</v>
+        <v>88989</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130163680</v>
       </c>
       <c r="B33" t="n">
-        <v>92742</v>
+        <v>92745</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>130163673</v>
       </c>
       <c r="B34" t="n">
-        <v>92742</v>
+        <v>92745</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92446</v>
+        <v>92449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92742</v>
+        <v>92745</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>88986</v>
+        <v>88989</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>88989</v>
+        <v>89015</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>101017</v>
+        <v>101043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>88989</v>
+        <v>89015</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130163680</v>
+        <v>130163673</v>
       </c>
       <c r="B33" t="n">
-        <v>92745</v>
+        <v>92771</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472621</v>
+        <v>472642</v>
       </c>
       <c r="R33" t="n">
-        <v>7016967</v>
+        <v>7016959</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130163673</v>
+        <v>130163680</v>
       </c>
       <c r="B34" t="n">
-        <v>92745</v>
+        <v>92771</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472642</v>
+        <v>472621</v>
       </c>
       <c r="R34" t="n">
-        <v>7016959</v>
+        <v>7016967</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92745</v>
+        <v>92771</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>88989</v>
+        <v>89015</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>89015</v>
+        <v>89016</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>101043</v>
+        <v>101044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>89015</v>
+        <v>89016</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130163673</v>
+        <v>130163680</v>
       </c>
       <c r="B33" t="n">
-        <v>92771</v>
+        <v>92772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472642</v>
+        <v>472621</v>
       </c>
       <c r="R33" t="n">
-        <v>7016959</v>
+        <v>7016967</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4263,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130163680</v>
+        <v>130163673</v>
       </c>
       <c r="B34" t="n">
-        <v>92771</v>
+        <v>92772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472621</v>
+        <v>472642</v>
       </c>
       <c r="R34" t="n">
-        <v>7016967</v>
+        <v>7016959</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92771</v>
+        <v>92772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>89015</v>
+        <v>89016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>89016</v>
+        <v>89017</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>101044</v>
+        <v>101045</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>89016</v>
+        <v>89017</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130163680</v>
       </c>
       <c r="B33" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>130163673</v>
       </c>
       <c r="B34" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>89016</v>
+        <v>89017</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -3862,7 +3862,7 @@
         <v>130163684</v>
       </c>
       <c r="B30" t="n">
-        <v>89017</v>
+        <v>89019</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>130163683</v>
       </c>
       <c r="B31" t="n">
-        <v>101045</v>
+        <v>101047</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>130163726</v>
       </c>
       <c r="B32" t="n">
-        <v>89017</v>
+        <v>89019</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         <v>130163680</v>
       </c>
       <c r="B33" t="n">
-        <v>92773</v>
+        <v>92775</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>130163673</v>
       </c>
       <c r="B34" t="n">
-        <v>92773</v>
+        <v>92775</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>130163716</v>
       </c>
       <c r="B35" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>130163705</v>
       </c>
       <c r="B36" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>130163677</v>
       </c>
       <c r="B37" t="n">
-        <v>92773</v>
+        <v>92775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>130163679</v>
       </c>
       <c r="B38" t="n">
-        <v>89017</v>
+        <v>89019</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100273193</v>
+        <v>100261874</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergom, Jmt</t>
+          <t>Maurmyren N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472632.1242771775</v>
+        <v>472623</v>
       </c>
       <c r="R2" t="n">
-        <v>7017001.030065082</v>
+        <v>7016977</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,24 +744,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackat i flertalet träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,12 +761,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -803,12 +776,7 @@
         <v>100273224</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472615.9590389075</v>
+        <v>472616</v>
       </c>
       <c r="R3" t="n">
-        <v>7017007.918333723</v>
+        <v>7017008</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,19 +844,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,12 +877,7 @@
         <v>100273244</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472641.9952012078</v>
+        <v>472642</v>
       </c>
       <c r="R4" t="n">
-        <v>7016942.889206309</v>
+        <v>7016943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +945,9 @@
           <t>2022-04-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100261874</v>
+        <v>100630318</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,20 +1004,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Maurmyren N, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472622.4542844165</v>
+        <v>472626</v>
       </c>
       <c r="R5" t="n">
-        <v>7016976.809555593</v>
+        <v>7017107</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,66 +1060,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100262304</v>
+        <v>100630342</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Maurmyren N, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472599.5808324747</v>
+        <v>472623</v>
       </c>
       <c r="R6" t="n">
-        <v>7017042.711324381</v>
+        <v>7017099</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,22 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,49 +1157,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100630352</v>
+        <v>100630344</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472647.5076814909</v>
+        <v>472657</v>
       </c>
       <c r="R7" t="n">
-        <v>7017061.205340338</v>
+        <v>7017078</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,19 +1237,9 @@
           <t>2022-05-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,53 +1266,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100630344</v>
+        <v>100636360</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>2063</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Maurmyren N , Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472657.1160529346</v>
+        <v>472645</v>
       </c>
       <c r="R8" t="n">
-        <v>7017078.225194664</v>
+        <v>7017107</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,26 +1337,21 @@
           <t>2022-05-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-08</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
@@ -1470,62 +1359,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100630342</v>
+        <v>130163705</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472623.0412827233</v>
+        <v>472664</v>
       </c>
       <c r="R9" t="n">
-        <v>7017098.76661966</v>
+        <v>7017017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,22 +1436,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,27 +1456,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100630324</v>
+        <v>130163679</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,42 +1483,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472677.2713622819</v>
+        <v>472621</v>
       </c>
       <c r="R10" t="n">
-        <v>7017010.547465213</v>
+        <v>7016967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,27 +1537,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,62 +1557,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100630333</v>
+        <v>130163684</v>
       </c>
       <c r="B11" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>4412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472599.9279913948</v>
+        <v>472663</v>
       </c>
       <c r="R11" t="n">
-        <v>7017030.557160739</v>
+        <v>7017050</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,22 +1638,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,27 +1658,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100630318</v>
+        <v>130163726</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,34 +1685,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472625.8138939267</v>
+        <v>472623</v>
       </c>
       <c r="R12" t="n">
-        <v>7017106.843667744</v>
+        <v>7016999</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,22 +1739,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,62 +1759,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100630306</v>
+        <v>130163673</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5836</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rödön Östra, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472680.3916061495</v>
+        <v>472642</v>
       </c>
       <c r="R13" t="n">
-        <v>7017059.575846612</v>
+        <v>7016959</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,22 +1840,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,68 +1860,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100636360</v>
+        <v>130163677</v>
       </c>
       <c r="B14" t="n">
-        <v>89734</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2063</v>
+        <v>5836</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Maurmyren N , Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472644.7435644343</v>
+        <v>472621</v>
       </c>
       <c r="R14" t="n">
-        <v>7017107.132711275</v>
+        <v>7016953</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,22 +1941,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,11 +1954,6 @@
       </c>
       <c r="AE14" t="b">
         <v>0</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2163,62 +1961,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103416863</v>
+        <v>130163680</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5836</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472677.3289625342</v>
+        <v>472621</v>
       </c>
       <c r="R15" t="n">
-        <v>7017070.402824851</v>
+        <v>7016967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,22 +2042,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,27 +2062,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103416860</v>
+        <v>100262304</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,37 +2089,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Maurmyren N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472633.5422355297</v>
+        <v>472600</v>
       </c>
       <c r="R16" t="n">
-        <v>7017061.774128616</v>
+        <v>7017043</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,22 +2144,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,62 +2164,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall, Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103416862</v>
+        <v>100630306</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472660.568064555</v>
+        <v>472681</v>
       </c>
       <c r="R17" t="n">
-        <v>7017060.194261331</v>
+        <v>7017060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,22 +2241,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,57 +2266,60 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103416861</v>
+        <v>100273193</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Bergom, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472634.4281698696</v>
+        <v>472632</v>
       </c>
       <c r="R18" t="n">
-        <v>7017059.966428795</v>
+        <v>7017001</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,22 +2346,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hackat i flertalet träd</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,50 +2383,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103416852</v>
+        <v>100630323</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472641.5033336079</v>
+        <v>472664</v>
       </c>
       <c r="R19" t="n">
-        <v>7016991.04920071</v>
+        <v>7017115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,22 +2456,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,57 +2486,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103416865</v>
+        <v>100630324</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472671.1234738482</v>
+        <v>472677</v>
       </c>
       <c r="R20" t="n">
-        <v>7017082.606576859</v>
+        <v>7017010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,22 +2566,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,57 +2596,60 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103416851</v>
+        <v>100630325</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Rödön Östra, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472625.9062170747</v>
+        <v>472589</v>
       </c>
       <c r="R21" t="n">
-        <v>7016958.778017456</v>
+        <v>7017042</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,22 +2676,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,57 +2706,52 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Benny Öwre, Johan Råghall</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103416866</v>
+        <v>130163749</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergom - Rödön, Jmt</t>
+          <t>Bergom kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472676.0879226613</v>
+        <v>472679</v>
       </c>
       <c r="R22" t="n">
-        <v>7017083.464491311</v>
+        <v>7017123</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,22 +2778,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,49 +2798,48 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103416855</v>
+        <v>103636876</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3111,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472664.4975015198</v>
+        <v>472584</v>
       </c>
       <c r="R23" t="n">
-        <v>7017045.309480619</v>
+        <v>7016997</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,22 +2879,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,15 +2911,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103416854</v>
+        <v>103416851</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,10 +2946,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472653.0444967248</v>
+        <v>472626</v>
       </c>
       <c r="R24" t="n">
-        <v>7017023.354599473</v>
+        <v>7016959</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,19 +2979,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,15 +3008,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103416857</v>
+        <v>103416852</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3335,10 +3043,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472641.5042019793</v>
+        <v>472641</v>
       </c>
       <c r="R25" t="n">
-        <v>7017044.154770144</v>
+        <v>7016991</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,19 +3076,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,12 +3108,7 @@
         <v>103416853</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472634.9199100436</v>
+        <v>472635</v>
       </c>
       <c r="R26" t="n">
-        <v>7017011.807460665</v>
+        <v>7017012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3480,19 +3173,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,56 +3202,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103415589</v>
+        <v>103416854</v>
       </c>
       <c r="B27" t="n">
-        <v>86210</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Maurmyren, Maurmyren, Rödön, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472651.563277045</v>
+        <v>472653</v>
       </c>
       <c r="R27" t="n">
-        <v>7017061.170867275</v>
+        <v>7017023</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3592,22 +3267,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3616,34 +3281,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103416864</v>
+        <v>103416855</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472662.0652189358</v>
+        <v>472665</v>
       </c>
       <c r="R28" t="n">
-        <v>7017077.283063688</v>
+        <v>7017045</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,19 +3367,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,15 +3396,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103416858</v>
+        <v>103416857</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,10 +3431,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472621.6652541948</v>
+        <v>472642</v>
       </c>
       <c r="R29" t="n">
-        <v>7017042.973382167</v>
+        <v>7017044</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3820,19 +3464,9 @@
           <t>2022-08-31</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,45 +3493,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130163684</v>
+        <v>103416858</v>
       </c>
       <c r="B30" t="n">
-        <v>89019</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472663</v>
+        <v>472621</v>
       </c>
       <c r="R30" t="n">
-        <v>7017050</v>
+        <v>7017043</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3924,12 +3558,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3944,61 +3578,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130163683</v>
+        <v>103416860</v>
       </c>
       <c r="B31" t="n">
-        <v>101047</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472654</v>
+        <v>472633</v>
       </c>
       <c r="R31" t="n">
-        <v>7017005</v>
+        <v>7017062</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,12 +3655,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,61 +3675,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130163726</v>
+        <v>103416861</v>
       </c>
       <c r="B32" t="n">
-        <v>89019</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472623</v>
+        <v>472635</v>
       </c>
       <c r="R32" t="n">
-        <v>7016999</v>
+        <v>7017060</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,12 +3752,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4146,61 +3772,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130163680</v>
+        <v>103416862</v>
       </c>
       <c r="B33" t="n">
-        <v>92775</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5836</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472621</v>
+        <v>472660</v>
       </c>
       <c r="R33" t="n">
-        <v>7016967</v>
+        <v>7017060</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4227,12 +3849,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4247,61 +3869,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130163673</v>
+        <v>103416863</v>
       </c>
       <c r="B34" t="n">
-        <v>92775</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5836</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472642</v>
+        <v>472678</v>
       </c>
       <c r="R34" t="n">
-        <v>7016959</v>
+        <v>7017071</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4328,12 +3946,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4348,26 +3966,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130163716</v>
+        <v>103416864</v>
       </c>
       <c r="B35" t="n">
-        <v>98953</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,14 +4009,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472630</v>
+        <v>472662</v>
       </c>
       <c r="R35" t="n">
-        <v>7017062</v>
+        <v>7017077</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4429,12 +4043,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4449,61 +4063,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130163705</v>
+        <v>103416865</v>
       </c>
       <c r="B36" t="n">
-        <v>92479</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472664</v>
+        <v>472671</v>
       </c>
       <c r="R36" t="n">
-        <v>7017017</v>
+        <v>7017082</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4530,12 +4140,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4550,61 +4160,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130163677</v>
+        <v>103416866</v>
       </c>
       <c r="B37" t="n">
-        <v>92775</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5836</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472621</v>
+        <v>472676</v>
       </c>
       <c r="R37" t="n">
-        <v>7016953</v>
+        <v>7017083</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4631,12 +4237,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4651,61 +4257,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Staaf, Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130163679</v>
+        <v>103636921</v>
       </c>
       <c r="B38" t="n">
-        <v>89019</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4412</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergom kalkbarrskog, Jmt</t>
+          <t>Bergom - Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472621</v>
+        <v>472624</v>
       </c>
       <c r="R38" t="n">
-        <v>7016967</v>
+        <v>7016920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4732,12 +4334,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4752,19 +4354,732 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>103636923</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bergom - Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>472602</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7016939</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>103636924</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bergom - Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>472588</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7016948</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130163716</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bergom kalkbarrskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>472630</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7017062</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Johan Staaf, Thomas Stålhandske</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
+      <c r="AY41" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130163683</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bergom kalkbarrskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>472654</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7017005</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>103416847</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bergom - Rödön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>472682</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7017094</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130163729</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bergom kalkbarrskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>472675</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7017109</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>100630333</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rödön Östra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>472600</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7017030</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-05-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55352-2021 artfynd.xlsx
+++ b/artfynd/A 55352-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100261874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100273224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100273244</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630344</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100636360</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163679</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163684</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163726</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163677</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163680</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2173,6 +2248,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100262304</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2380,6 +2465,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100273193</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630323</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2600,6 +2695,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630324</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630325</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2811,6 +2916,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163749</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2908,6 +3018,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103636876</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,6 +3120,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416851</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416852</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3199,6 +3324,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416853</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416854</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3393,6 +3528,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416855</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3490,6 +3630,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416857</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3587,6 +3732,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416858</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3684,6 +3834,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416860</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3781,6 +3936,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416861</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3878,6 +4038,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416862</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3975,6 +4140,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416863</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4072,6 +4242,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416864</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4169,6 +4344,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416865</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4266,6 +4446,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416866</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4363,6 +4548,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103636921</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4473,6 +4663,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103636923</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4583,6 +4778,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103636924</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4684,6 +4884,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163716</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4785,6 +4990,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163683</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4882,6 +5092,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103416847</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2024</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130163729</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5080,8 +5300,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100630333</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>